--- a/ADMA_CAIQ_v4.0.3_Completed_2026-08-31.xlsx
+++ b/ADMA_CAIQ_v4.0.3_Completed_2026-08-31.xlsx
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys.</t>
+          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys. UPDATE 2026-08-31: stale evidence corrected — KEY_MANAGEMENT_POLICY.md (effective 2026-08-05) has existed for 26 days but was never cross-applied to this row. Sec 1/2 document AES-256 at rest (DynamoDB/S3 default encryption) and TLS 1.2+ in transit (Let's Encrypt via nginx, HSTS enforced) — both industry-approved standards, matching the identical reasoning already credited to CEK-04.1.</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>No formal key management policy, rotation schedule, or HSM/KMS customer-managed key usage — relies on AWS-managed default keys.</t>
+          <t>No formal key management policy, rotation schedule, or HSM/KMS customer-managed key usage — relies on AWS-managed default keys. UPDATE 2026-08-31: evidence corrected — KEY_MANAGEMENT_POLICY.md exists (see CEK-01.1), so "no formal key management policy" is stale. Stays No on the real remaining gap: CHANGE_MANAGEMENT.md's general change process (cited at CEK-05.1) does not include a formal cost/benefit or residual-risk analysis step specifically for crypto/key changes.</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys.</t>
+          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys. UPDATE 2026-08-31: evidence corrected — a key management policy exists (see CEK-01.1), so "no documented policy" is stale. Stays Partial on the real gap this question actually asks about: CSCs (exhibitors) have no self-service capability to manage their own data encryption keys at all — this question is about a customer-facing capability ADMA doesn't offer, not about ADMA's own internal key documentation.</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>No formal key management policy, rotation schedule, or HSM/KMS customer-managed key usage — relies on AWS-managed default keys.</t>
+          <t>No formal key management policy, rotation schedule, or HSM/KMS customer-managed key usage — relies on AWS-managed default keys. UPDATE 2026-08-31: evidence corrected — a key management policy exists (see CEK-01.1). Stays No on the real gap: Sec 5's annual review commitment is self-review, not an independent audit proportional to risk exposure — same distinction this document applies consistently to Audit &amp; Assurance's "independent" bar.</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>No formal key management policy, rotation schedule, or HSM/KMS customer-managed key usage — relies on AWS-managed default keys.</t>
+          <t>No formal key management policy, rotation schedule, or HSM/KMS customer-managed key usage — relies on AWS-managed default keys. UPDATE 2026-08-31: evidence corrected — same distinction as CEK-09.1. Sec 5 commits to an annual self-review; this question asks about audit specifically, which self-review does not satisfy.</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr"/>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys.</t>
+          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys. UPDATE 2026-08-31: stale evidence corrected — same cross-application gap as CEK-03.1. KEY_MANAGEMENT_POLICY.md Sec 3's table catalogues each distinct secret/key type (passwords, TOTP secrets, session tokens, third-party API keys) with its own protection mechanism, matching the identical reasoning already credited to CEK-10.1 and CEK-21.1.</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>No formal key management policy, rotation schedule, or HSM/KMS customer-managed key usage — relies on AWS-managed default keys.</t>
+          <t>No formal key management policy, rotation schedule, or HSM/KMS customer-managed key usage — relies on AWS-managed default keys. UPDATE 2026-08-31: evidence corrected — a key management policy exists (see CEK-01.1), but it explicitly and honestly flags this exact gap itself: Sec 6 Open Items states "no periodic rotation happens" for server/.env secrets. Correctly stays No — the policy documents the absence of rotation rather than papering over it.</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>No formal key management policy, rotation schedule, or HSM/KMS customer-managed key usage — relies on AWS-managed default keys.</t>
+          <t>No formal key management policy, rotation schedule, or HSM/KMS customer-managed key usage — relies on AWS-managed default keys. UPDATE 2026-08-31: evidence corrected — a key management policy exists (see CEK-01.1) but does not define a key destruction process; stays No on that real, unaddressed gap.</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys.</t>
+          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys. UPDATE 2026-08-31: evidence corrected — a key management policy exists (see CEK-01.1) and Sec 3 documents where each secret lives and how it's protected, but doesn't define a formal pre-activation state/process for keys specifically. Stays Partial.</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys.</t>
+          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys. UPDATE 2026-08-31: evidence corrected — same as CEK-15.1; no formal suspension-state process defined. Stays Partial.</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys.</t>
+          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys. UPDATE 2026-08-31: evidence corrected — same as CEK-15.1; no formal expiration-triggered deactivation process defined (rotation itself is an acknowledged open item, see CEK-12.1). Stays Partial.</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys.</t>
+          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys. UPDATE 2026-08-31: evidence corrected — Sec 3's table is a real, if lightweight, inventory of where secrets live, but there's no formal secure-archival-repository process for retired keys specifically. Stays Partial.</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys.</t>
+          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys. UPDATE 2026-08-31: evidence corrected — a key management policy exists (see CEK-01.1), and ONBOARDING_OFFBOARDING.md's revocation-on-departure step (cited at CEK-13.1) is the closest real analog, but there's no formal "compromised key: decrypt-only, never re-encrypt" procedure. Stays Partial.</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys.</t>
+          <t>TLS in transit and AWS default encryption at rest are in place, but there is no documented key management policy, key rotation schedule, or customer-managed keys. UPDATE 2026-08-31: evidence corrected — a key management policy exists (see CEK-01.1), but no formal operational-continuity-vs-key-loss risk assessment process is defined beyond RISK_REGISTER.md #8's general treatment of the customer-managed-KMS question. Stays Partial.</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
